--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137044069</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>137044076</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,51 +1073,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137044067</v>
+        <v>137040119</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>92549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636906</v>
+        <v>636916</v>
       </c>
       <c r="R5" t="n">
-        <v>7014210</v>
+        <v>7014230</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,90 +1162,71 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044067</t>
+          <t>https://artportalen.se/Sighting/137040119</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137044068</v>
+        <v>137040165</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>92950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636901</v>
+        <v>636776</v>
       </c>
       <c r="R6" t="n">
-        <v>7014208</v>
+        <v>7014299</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1287,7 +1265,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,49 +1279,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044068</t>
+          <t>https://artportalen.se/Sighting/137040165</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137044072</v>
+        <v>137040167</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,19 +1331,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636840</v>
+        <v>636743</v>
       </c>
       <c r="R7" t="n">
-        <v>7014233</v>
+        <v>7014374</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1408,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1418,7 +1382,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,49 +1391,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044072</t>
+          <t>https://artportalen.se/Sighting/137040167</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137044074</v>
+        <v>137040169</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,22 +1443,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636748</v>
+        <v>636844</v>
       </c>
       <c r="R8" t="n">
-        <v>7014429</v>
+        <v>7014273</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1539,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1549,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1558,49 +1503,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044074</t>
+          <t>https://artportalen.se/Sighting/137040169</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137044078</v>
+        <v>137040172</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,22 +1555,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636645</v>
+        <v>636917</v>
       </c>
       <c r="R9" t="n">
-        <v>7014500</v>
+        <v>7014256</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1670,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1680,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1689,49 +1615,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044078</t>
+          <t>https://artportalen.se/Sighting/137040172</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137044079</v>
+        <v>137040174</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1757,22 +1667,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636642</v>
+        <v>636903</v>
       </c>
       <c r="R10" t="n">
-        <v>7014500</v>
+        <v>7014213</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1801,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1811,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,71 +1727,55 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044079</t>
+          <t>https://artportalen.se/Sighting/137040174</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137044081</v>
+        <v>137040175</v>
       </c>
       <c r="B11" t="n">
-        <v>79237</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1894,13 +1785,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636578</v>
+        <v>636957</v>
       </c>
       <c r="R11" t="n">
-        <v>7014624</v>
+        <v>7014152</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1929,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1939,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1948,79 +1839,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044081</t>
+          <t>https://artportalen.se/Sighting/137040175</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137044090</v>
+        <v>137040181</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636396</v>
+        <v>636605</v>
       </c>
       <c r="R12" t="n">
-        <v>7014799</v>
+        <v>7014506</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2049,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2059,12 +1943,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>Garnlav på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2079,73 +1963,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044090</t>
+          <t>https://artportalen.se/Sighting/137040181</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137044091</v>
+        <v>137040183</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636412</v>
+        <v>636428</v>
       </c>
       <c r="R13" t="n">
-        <v>7014771</v>
+        <v>7014785</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2174,7 +2050,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2184,12 +2060,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2204,27 +2080,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044091</t>
+          <t>https://artportalen.se/Sighting/137040183</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137044059</v>
+        <v>137044067</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2232,35 +2108,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2268,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636736</v>
+        <v>636906</v>
       </c>
       <c r="R14" t="n">
-        <v>7014341</v>
+        <v>7014210</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2303,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2313,7 +2180,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2326,6 +2193,21 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
@@ -2334,22 +2216,22 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044059</t>
+          <t>https://artportalen.se/Sighting/137044067</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137044060</v>
+        <v>137044068</v>
       </c>
       <c r="B15" t="n">
-        <v>99359</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,35 +2239,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2393,10 +2266,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636760</v>
+        <v>636901</v>
       </c>
       <c r="R15" t="n">
-        <v>7014309</v>
+        <v>7014208</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2428,7 +2301,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2438,7 +2311,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2451,6 +2324,21 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2459,22 +2347,22 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044060</t>
+          <t>https://artportalen.se/Sighting/137044068</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137044061</v>
+        <v>137044072</v>
       </c>
       <c r="B16" t="n">
-        <v>99359</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2482,35 +2370,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2518,10 +2397,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636781</v>
+        <v>636840</v>
       </c>
       <c r="R16" t="n">
-        <v>7014323</v>
+        <v>7014233</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2553,7 +2432,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2563,7 +2442,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2576,6 +2455,21 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
@@ -2584,22 +2478,22 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044061</t>
+          <t>https://artportalen.se/Sighting/137044072</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137044062</v>
+        <v>137044074</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2607,35 +2501,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2643,10 +2528,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636772</v>
+        <v>636748</v>
       </c>
       <c r="R17" t="n">
-        <v>7014326</v>
+        <v>7014429</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2678,7 +2563,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2688,7 +2573,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2701,6 +2586,21 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
@@ -2709,22 +2609,22 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044062</t>
+          <t>https://artportalen.se/Sighting/137044074</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137044064</v>
+        <v>137044078</v>
       </c>
       <c r="B18" t="n">
-        <v>99359</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2732,35 +2632,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2768,10 +2659,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636806</v>
+        <v>636645</v>
       </c>
       <c r="R18" t="n">
-        <v>7014282</v>
+        <v>7014500</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2803,7 +2694,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2813,7 +2704,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2826,6 +2717,21 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
@@ -2834,22 +2740,22 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044064</t>
+          <t>https://artportalen.se/Sighting/137044078</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137044073</v>
+        <v>137044079</v>
       </c>
       <c r="B19" t="n">
-        <v>99359</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2857,35 +2763,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2893,10 +2790,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636823</v>
+        <v>636642</v>
       </c>
       <c r="R19" t="n">
-        <v>7014305</v>
+        <v>7014500</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2928,7 +2825,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2938,7 +2835,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2951,6 +2848,21 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2959,69 +2871,57 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044073</t>
+          <t>https://artportalen.se/Sighting/137044079</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137044075</v>
+        <v>137044081</v>
       </c>
       <c r="B20" t="n">
-        <v>99359</v>
+        <v>79239</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636709</v>
+        <v>636578</v>
       </c>
       <c r="R20" t="n">
-        <v>7014464</v>
+        <v>7014624</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3053,7 +2953,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3063,7 +2963,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3072,7 +2972,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3084,58 +2983,54 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044075</t>
+          <t>https://artportalen.se/Sighting/137044081</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137044080</v>
+        <v>137044090</v>
       </c>
       <c r="B21" t="n">
-        <v>99359</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3143,10 +3038,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636598</v>
+        <v>636396</v>
       </c>
       <c r="R21" t="n">
-        <v>7014517</v>
+        <v>7014799</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3178,7 +3073,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3188,7 +3083,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3197,7 +3097,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3215,52 +3114,48 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044080</t>
+          <t>https://artportalen.se/Sighting/137044090</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137044083</v>
+        <v>137044091</v>
       </c>
       <c r="B22" t="n">
-        <v>99359</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3268,10 +3163,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636563</v>
+        <v>636412</v>
       </c>
       <c r="R22" t="n">
-        <v>7014676</v>
+        <v>7014771</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3303,7 +3198,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3313,7 +3208,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3322,7 +3222,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3340,52 +3239,48 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044083</t>
+          <t>https://artportalen.se/Sighting/137044091</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137044086</v>
+        <v>137040176</v>
       </c>
       <c r="B23" t="n">
-        <v>99359</v>
+        <v>57195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3393,13 +3288,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636541</v>
+        <v>636938</v>
       </c>
       <c r="R23" t="n">
-        <v>7014733</v>
+        <v>7014209</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3428,7 +3323,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3438,7 +3333,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fjädrar på marken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3447,70 +3347,65 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044086</t>
+          <t>https://artportalen.se/Sighting/137040176</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137044089</v>
+        <v>137040177</v>
       </c>
       <c r="B24" t="n">
-        <v>99359</v>
+        <v>58169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3518,13 +3413,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636403</v>
+        <v>636811</v>
       </c>
       <c r="R24" t="n">
-        <v>7014809</v>
+        <v>7014284</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3448,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3458,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3572,70 +3472,69 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044089</t>
+          <t>https://artportalen.se/Sighting/137040177</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137044092</v>
+        <v>137040187</v>
       </c>
       <c r="B25" t="n">
-        <v>99359</v>
+        <v>58169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3643,13 +3542,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636418</v>
+        <v>636402</v>
       </c>
       <c r="R25" t="n">
-        <v>7014750</v>
+        <v>7014762</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3678,7 +3577,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3688,7 +3587,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Såg talltita</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3697,34 +3601,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044092</t>
+          <t>https://artportalen.se/Sighting/137040187</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137044093</v>
+        <v>137040166</v>
       </c>
       <c r="B26" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3751,7 +3654,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3768,13 +3671,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636379</v>
+        <v>636782</v>
       </c>
       <c r="R26" t="n">
-        <v>7014720</v>
+        <v>7014300</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3803,7 +3706,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3813,7 +3716,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3829,65 +3732,77 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044093</t>
+          <t>https://artportalen.se/Sighting/137040166</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137044065</v>
+        <v>137040168</v>
       </c>
       <c r="B27" t="n">
-        <v>98221</v>
+        <v>99361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636909</v>
+        <v>636758</v>
       </c>
       <c r="R27" t="n">
-        <v>7014251</v>
+        <v>7014368</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3916,7 +3831,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3926,7 +3841,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3935,71 +3850,84 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044065</t>
+          <t>https://artportalen.se/Sighting/137040168</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137044077</v>
+        <v>137040170</v>
       </c>
       <c r="B28" t="n">
-        <v>98221</v>
+        <v>99361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636674</v>
+        <v>636884</v>
       </c>
       <c r="R28" t="n">
-        <v>7014469</v>
+        <v>7014281</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4028,7 +3956,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4038,7 +3966,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4047,71 +3975,84 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044077</t>
+          <t>https://artportalen.se/Sighting/137040170</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137044087</v>
+        <v>137040178</v>
       </c>
       <c r="B29" t="n">
-        <v>98221</v>
+        <v>99361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636457</v>
+        <v>636758</v>
       </c>
       <c r="R29" t="n">
-        <v>7014788</v>
+        <v>7014394</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4140,7 +4081,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4150,7 +4091,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4159,71 +4100,84 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044087</t>
+          <t>https://artportalen.se/Sighting/137040178</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137044088</v>
+        <v>137040180</v>
       </c>
       <c r="B30" t="n">
-        <v>98221</v>
+        <v>99361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636399</v>
+        <v>636672</v>
       </c>
       <c r="R30" t="n">
-        <v>7014848</v>
+        <v>7014492</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4252,7 +4206,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4262,7 +4216,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4271,64 +4225,70 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044088</t>
+          <t>https://artportalen.se/Sighting/137040180</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137044066</v>
+        <v>137040186</v>
       </c>
       <c r="B31" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4336,13 +4296,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636899</v>
+        <v>636390</v>
       </c>
       <c r="R31" t="n">
-        <v>7014254</v>
+        <v>7014777</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4371,7 +4331,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4381,7 +4341,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4394,76 +4354,66 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044066</t>
+          <t>https://artportalen.se/Sighting/137040186</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137044071</v>
+        <v>137040188</v>
       </c>
       <c r="B32" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4471,13 +4421,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636845</v>
+        <v>636412</v>
       </c>
       <c r="R32" t="n">
-        <v>7014233</v>
+        <v>7014689</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4506,7 +4456,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4516,7 +4466,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4529,76 +4479,66 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044071</t>
+          <t>https://artportalen.se/Sighting/137040188</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137044082</v>
+        <v>137040189</v>
       </c>
       <c r="B33" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4606,13 +4546,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636579</v>
+        <v>636424</v>
       </c>
       <c r="R33" t="n">
-        <v>7014650</v>
+        <v>7014610</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4641,7 +4581,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4651,7 +4591,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4664,34 +4604,2721 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040189</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137044059</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>636736</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7014341</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044059</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137044060</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>636760</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7014309</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044060</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137044061</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>636781</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7014323</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044061</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137044062</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>636772</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7014326</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044062</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137044064</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>636806</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7014282</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044064</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137044073</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>636823</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7014305</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044073</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137044075</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>636709</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7014464</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044075</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137044080</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>636598</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7014517</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044080</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137044083</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>636563</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7014676</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044083</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137044086</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>636541</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7014733</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044086</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137044089</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>636403</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7014809</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044089</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137044092</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>636418</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7014750</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044092</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137044093</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>636379</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7014720</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044093</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137040184</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>636401</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7014880</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040184</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137040185</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>636377</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7014865</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040185</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137044065</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>636909</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7014251</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044065</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137044077</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>636674</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7014469</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044077</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137044087</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>636457</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7014788</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044087</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137044088</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>636399</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7014848</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044088</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137044066</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>636899</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7014254</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044066</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137044071</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>636845</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7014233</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044071</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137044082</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>636579</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7014650</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137044082</t>
         </is>
@@ -4731,6 +7358,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>92950</v>
+        <v>92951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>137040133</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137040140</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137040141</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137040167</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137040169</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137040172</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137040174</v>
       </c>
       <c r="B23" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137040175</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>137040181</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137040183</v>
       </c>
       <c r="B26" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>137044067</v>
       </c>
       <c r="B27" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>137044068</v>
       </c>
       <c r="B28" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>137044072</v>
       </c>
       <c r="B29" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137044074</v>
       </c>
       <c r="B30" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>137044078</v>
       </c>
       <c r="B31" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137044079</v>
       </c>
       <c r="B32" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>137040113</v>
       </c>
       <c r="B33" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>137040128</v>
       </c>
       <c r="B34" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137040132</v>
       </c>
       <c r="B35" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>137040135</v>
       </c>
       <c r="B36" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>137044081</v>
       </c>
       <c r="B37" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>137040108</v>
       </c>
       <c r="B38" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137040110</v>
       </c>
       <c r="B39" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>137040111</v>
       </c>
       <c r="B40" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137040156</v>
       </c>
       <c r="B41" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>137040134</v>
       </c>
       <c r="B94" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>137040136</v>
       </c>
       <c r="B95" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>137040139</v>
       </c>
       <c r="B96" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>137044066</v>
       </c>
       <c r="B97" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>137044071</v>
       </c>
       <c r="B98" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>137044082</v>
       </c>
       <c r="B99" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>92951</v>
+        <v>92957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92510</v>
+        <v>92516</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7002,7 +7002,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7127,7 +7127,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7252,7 +7252,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7377,7 +7377,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7502,7 +7502,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7752,7 +7752,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7877,7 +7877,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8002,7 +8002,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8127,7 +8127,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8252,7 +8252,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10989,7 +10989,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -11101,7 +11101,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -11213,7 +11213,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>92961</v>
+        <v>92963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>137040133</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137040140</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137040141</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137040167</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137040169</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137040172</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137040174</v>
       </c>
       <c r="B23" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137040175</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>137040181</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137040183</v>
       </c>
       <c r="B26" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>137044067</v>
       </c>
       <c r="B27" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>137044068</v>
       </c>
       <c r="B28" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>137044072</v>
       </c>
       <c r="B29" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137044074</v>
       </c>
       <c r="B30" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>137044078</v>
       </c>
       <c r="B31" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137044079</v>
       </c>
       <c r="B32" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>137040113</v>
       </c>
       <c r="B33" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>137040128</v>
       </c>
       <c r="B34" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137040132</v>
       </c>
       <c r="B35" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>137040135</v>
       </c>
       <c r="B36" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>137044081</v>
       </c>
       <c r="B37" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>137040108</v>
       </c>
       <c r="B38" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137040110</v>
       </c>
       <c r="B39" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>137040111</v>
       </c>
       <c r="B40" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137040156</v>
       </c>
       <c r="B41" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>137040134</v>
       </c>
       <c r="B94" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>137040136</v>
       </c>
       <c r="B95" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>137040139</v>
       </c>
       <c r="B96" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>137044066</v>
       </c>
       <c r="B97" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>137044071</v>
       </c>
       <c r="B98" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>137044082</v>
       </c>
       <c r="B99" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137044069</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>137044076</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>137040119</v>
       </c>
       <c r="B5" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>137040165</v>
       </c>
       <c r="B6" t="n">
-        <v>92976</v>
+        <v>92978</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>137040167</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>137040169</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>137040172</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>137040174</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137040175</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>137040181</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137040183</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137044067</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>137044068</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>137044072</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>137044074</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>137044078</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>137044079</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>137044081</v>
       </c>
       <c r="B20" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>137044090</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137044091</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>137040176</v>
       </c>
       <c r="B23" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>137040177</v>
       </c>
       <c r="B24" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>137040187</v>
       </c>
       <c r="B25" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>137040166</v>
       </c>
       <c r="B26" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>137040168</v>
       </c>
       <c r="B27" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>137040170</v>
       </c>
       <c r="B28" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>137040178</v>
       </c>
       <c r="B29" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>137040180</v>
       </c>
       <c r="B30" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>137040186</v>
       </c>
       <c r="B31" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>137040188</v>
       </c>
       <c r="B32" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>137040189</v>
       </c>
       <c r="B33" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137044059</v>
       </c>
       <c r="B34" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>137044060</v>
       </c>
       <c r="B35" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>137044061</v>
       </c>
       <c r="B36" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137044062</v>
       </c>
       <c r="B37" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>137044064</v>
       </c>
       <c r="B38" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>137044073</v>
       </c>
       <c r="B39" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>137044075</v>
       </c>
       <c r="B40" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>137044080</v>
       </c>
       <c r="B41" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>137044083</v>
       </c>
       <c r="B42" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>137044086</v>
       </c>
       <c r="B43" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>137044089</v>
       </c>
       <c r="B44" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>137044092</v>
       </c>
       <c r="B45" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137044093</v>
       </c>
       <c r="B46" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>137040184</v>
       </c>
       <c r="B47" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>137040185</v>
       </c>
       <c r="B48" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>137044065</v>
       </c>
       <c r="B49" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>137044077</v>
       </c>
       <c r="B50" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>137044087</v>
       </c>
       <c r="B51" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>137044088</v>
       </c>
       <c r="B52" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>137044066</v>
       </c>
       <c r="B53" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>137044071</v>
       </c>
       <c r="B54" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>137044082</v>
       </c>
       <c r="B55" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>92978</v>
+        <v>92981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92537</v>
+        <v>92540</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>92981</v>
+        <v>92991</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>137040133</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137040140</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137040141</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137040167</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137040169</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137040172</v>
       </c>
       <c r="B22" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137040174</v>
       </c>
       <c r="B23" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137040175</v>
       </c>
       <c r="B24" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>137040181</v>
       </c>
       <c r="B25" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137040183</v>
       </c>
       <c r="B26" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>137044067</v>
       </c>
       <c r="B27" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>137044068</v>
       </c>
       <c r="B28" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>137044072</v>
       </c>
       <c r="B29" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137044074</v>
       </c>
       <c r="B30" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>137044078</v>
       </c>
       <c r="B31" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137044079</v>
       </c>
       <c r="B32" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>137040113</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>137040128</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137040132</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>137040135</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>137044081</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>137040108</v>
       </c>
       <c r="B38" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137040110</v>
       </c>
       <c r="B39" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>137040111</v>
       </c>
       <c r="B40" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137040156</v>
       </c>
       <c r="B41" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>137040124</v>
       </c>
       <c r="B42" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137040158</v>
       </c>
       <c r="B43" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>137044090</v>
       </c>
       <c r="B44" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>137044091</v>
       </c>
       <c r="B45" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>137040176</v>
       </c>
       <c r="B46" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>137040106</v>
       </c>
       <c r="B47" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137040109</v>
       </c>
       <c r="B48" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>137040127</v>
       </c>
       <c r="B49" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>137040152</v>
       </c>
       <c r="B50" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>137040177</v>
       </c>
       <c r="B51" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>137040187</v>
       </c>
       <c r="B52" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>137040154</v>
       </c>
       <c r="B53" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>137040134</v>
       </c>
       <c r="B94" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>137040136</v>
       </c>
       <c r="B95" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>137040139</v>
       </c>
       <c r="B96" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>137044066</v>
       </c>
       <c r="B97" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>137044071</v>
       </c>
       <c r="B98" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>137044082</v>
       </c>
       <c r="B99" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92540</v>
+        <v>92550</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>92991</v>
+        <v>92992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>92992</v>
+        <v>92995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>137040133</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2576,7 +2576,7 @@
         <v>137040140</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
         <v>137040141</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2838,7 +2838,7 @@
         <v>137040167</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137040169</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137040172</v>
       </c>
       <c r="B22" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137040174</v>
       </c>
       <c r="B23" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137040175</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>137040181</v>
       </c>
       <c r="B25" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137040183</v>
       </c>
       <c r="B26" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>137044067</v>
       </c>
       <c r="B27" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>137044068</v>
       </c>
       <c r="B28" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>137044072</v>
       </c>
       <c r="B29" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137044074</v>
       </c>
       <c r="B30" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>137044078</v>
       </c>
       <c r="B31" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137044079</v>
       </c>
       <c r="B32" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>137040113</v>
       </c>
       <c r="B33" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>137040128</v>
       </c>
       <c r="B34" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4647,7 +4647,7 @@
         <v>137040132</v>
       </c>
       <c r="B35" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>137040135</v>
       </c>
       <c r="B36" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>137044081</v>
       </c>
       <c r="B37" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>137040108</v>
       </c>
       <c r="B38" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
         <v>137040110</v>
       </c>
       <c r="B39" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5245,7 +5245,7 @@
         <v>137040111</v>
       </c>
       <c r="B40" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
         <v>137040156</v>
       </c>
       <c r="B41" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5507,7 +5507,7 @@
         <v>137040124</v>
       </c>
       <c r="B42" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5628,7 +5628,7 @@
         <v>137040158</v>
       </c>
       <c r="B43" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5749,7 +5749,7 @@
         <v>137044090</v>
       </c>
       <c r="B44" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>137044091</v>
       </c>
       <c r="B45" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>137040176</v>
       </c>
       <c r="B46" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>137040106</v>
       </c>
       <c r="B47" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6236,7 +6236,7 @@
         <v>137040109</v>
       </c>
       <c r="B48" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>137040127</v>
       </c>
       <c r="B49" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>137040152</v>
       </c>
       <c r="B50" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>137040177</v>
       </c>
       <c r="B51" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>137040187</v>
       </c>
       <c r="B52" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>137040154</v>
       </c>
       <c r="B53" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>137040134</v>
       </c>
       <c r="B94" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>137040136</v>
       </c>
       <c r="B95" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>137040139</v>
       </c>
       <c r="B96" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>137044066</v>
       </c>
       <c r="B97" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>137044071</v>
       </c>
       <c r="B98" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>137044082</v>
       </c>
       <c r="B99" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92551</v>
+        <v>92554</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>92995</v>
+        <v>92997</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>92997</v>
+        <v>93003</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>137040133</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137040140</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137040141</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137040167</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137040169</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137040172</v>
       </c>
       <c r="B22" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137040174</v>
       </c>
       <c r="B23" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137040175</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>137040181</v>
       </c>
       <c r="B25" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137040183</v>
       </c>
       <c r="B26" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>137044067</v>
       </c>
       <c r="B27" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>137044068</v>
       </c>
       <c r="B28" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>137044072</v>
       </c>
       <c r="B29" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137044074</v>
       </c>
       <c r="B30" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>137044078</v>
       </c>
       <c r="B31" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137044079</v>
       </c>
       <c r="B32" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>137040113</v>
       </c>
       <c r="B33" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>137040128</v>
       </c>
       <c r="B34" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137040132</v>
       </c>
       <c r="B35" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>137040135</v>
       </c>
       <c r="B36" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>137044081</v>
       </c>
       <c r="B37" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>137040108</v>
       </c>
       <c r="B38" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137040110</v>
       </c>
       <c r="B39" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>137040111</v>
       </c>
       <c r="B40" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137040156</v>
       </c>
       <c r="B41" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>137040124</v>
       </c>
       <c r="B42" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137040158</v>
       </c>
       <c r="B43" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>137044090</v>
       </c>
       <c r="B44" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>137044091</v>
       </c>
       <c r="B45" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>137040106</v>
       </c>
       <c r="B47" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137040109</v>
       </c>
       <c r="B48" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>137040127</v>
       </c>
       <c r="B49" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>137040152</v>
       </c>
       <c r="B50" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>137040177</v>
       </c>
       <c r="B51" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>137040187</v>
       </c>
       <c r="B52" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>137040154</v>
       </c>
       <c r="B53" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>137040134</v>
       </c>
       <c r="B94" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>137040136</v>
       </c>
       <c r="B95" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>137040139</v>
       </c>
       <c r="B96" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>137044066</v>
       </c>
       <c r="B97" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>137044071</v>
       </c>
       <c r="B98" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>137044082</v>
       </c>
       <c r="B99" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92556</v>
+        <v>92561</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>93003</v>
+        <v>93015</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>137040133</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137040140</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137040141</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137040167</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137040169</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137040172</v>
       </c>
       <c r="B22" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137040174</v>
       </c>
       <c r="B23" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137040175</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>137040181</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137040183</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>137044067</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>137044068</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>137044072</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137044074</v>
       </c>
       <c r="B30" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>137044078</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137044079</v>
       </c>
       <c r="B32" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>137040113</v>
       </c>
       <c r="B33" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>137040128</v>
       </c>
       <c r="B34" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137040132</v>
       </c>
       <c r="B35" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>137040135</v>
       </c>
       <c r="B36" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>137044081</v>
       </c>
       <c r="B37" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>137040108</v>
       </c>
       <c r="B38" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137040110</v>
       </c>
       <c r="B39" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>137040111</v>
       </c>
       <c r="B40" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137040156</v>
       </c>
       <c r="B41" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>137040134</v>
       </c>
       <c r="B94" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>137040136</v>
       </c>
       <c r="B95" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>137040139</v>
       </c>
       <c r="B96" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>137044066</v>
       </c>
       <c r="B97" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>137044071</v>
       </c>
       <c r="B98" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>137044082</v>
       </c>
       <c r="B99" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92561</v>
+        <v>92573</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>137040133</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137040140</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137040141</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137040167</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137040169</v>
       </c>
       <c r="B21" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137040172</v>
       </c>
       <c r="B22" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137040174</v>
       </c>
       <c r="B23" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137040175</v>
       </c>
       <c r="B24" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>137040181</v>
       </c>
       <c r="B25" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137040183</v>
       </c>
       <c r="B26" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>137044067</v>
       </c>
       <c r="B27" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>137044068</v>
       </c>
       <c r="B28" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>137044072</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137044074</v>
       </c>
       <c r="B30" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>137044078</v>
       </c>
       <c r="B31" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137044079</v>
       </c>
       <c r="B32" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>137040113</v>
       </c>
       <c r="B33" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>137040128</v>
       </c>
       <c r="B34" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137040132</v>
       </c>
       <c r="B35" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>137040135</v>
       </c>
       <c r="B36" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>137044081</v>
       </c>
       <c r="B37" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>137040108</v>
       </c>
       <c r="B38" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137040110</v>
       </c>
       <c r="B39" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>137040111</v>
       </c>
       <c r="B40" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137040156</v>
       </c>
       <c r="B41" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>137040134</v>
       </c>
       <c r="B94" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>137040136</v>
       </c>
       <c r="B95" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>137040139</v>
       </c>
       <c r="B96" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>137044066</v>
       </c>
       <c r="B97" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>137044071</v>
       </c>
       <c r="B98" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>137044082</v>
       </c>
       <c r="B99" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92573</v>
+        <v>92574</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>93016</v>
+        <v>93019</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>137040133</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137040140</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137040141</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137040167</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137040169</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137040172</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137040174</v>
       </c>
       <c r="B23" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137040175</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>137040181</v>
       </c>
       <c r="B25" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137040183</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>137044067</v>
       </c>
       <c r="B27" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>137044068</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>137044072</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137044074</v>
       </c>
       <c r="B30" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>137044078</v>
       </c>
       <c r="B31" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137044079</v>
       </c>
       <c r="B32" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>137040113</v>
       </c>
       <c r="B33" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>137040128</v>
       </c>
       <c r="B34" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137040132</v>
       </c>
       <c r="B35" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>137040135</v>
       </c>
       <c r="B36" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>137044081</v>
       </c>
       <c r="B37" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>137040108</v>
       </c>
       <c r="B38" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137040110</v>
       </c>
       <c r="B39" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>137040111</v>
       </c>
       <c r="B40" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137040156</v>
       </c>
       <c r="B41" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>137040134</v>
       </c>
       <c r="B94" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>137040136</v>
       </c>
       <c r="B95" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>137040139</v>
       </c>
       <c r="B96" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>137044066</v>
       </c>
       <c r="B97" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>137044071</v>
       </c>
       <c r="B98" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>137044082</v>
       </c>
       <c r="B99" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92574</v>
+        <v>92577</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 18696-2025 artfynd.xlsx
+++ b/artfynd/A 18696-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137040144</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137040151</v>
       </c>
       <c r="B3" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137040125</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137040129</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137044063</v>
       </c>
       <c r="B6" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>137044069</v>
       </c>
       <c r="B7" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137040115</v>
       </c>
       <c r="B8" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>137040120</v>
       </c>
       <c r="B9" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>137040130</v>
       </c>
       <c r="B10" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>137040150</v>
       </c>
       <c r="B11" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137044076</v>
       </c>
       <c r="B12" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>137040119</v>
       </c>
       <c r="B13" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>137040149</v>
       </c>
       <c r="B14" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>137040165</v>
       </c>
       <c r="B15" t="n">
-        <v>93019</v>
+        <v>93023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>137040122</v>
       </c>
       <c r="B16" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>137040133</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>137040140</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137040141</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137040167</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137040169</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137040172</v>
       </c>
       <c r="B22" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137040174</v>
       </c>
       <c r="B23" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137040175</v>
       </c>
       <c r="B24" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>137040181</v>
       </c>
       <c r="B25" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137040183</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>137044067</v>
       </c>
       <c r="B27" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>137044068</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>137044072</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137044074</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>137044078</v>
       </c>
       <c r="B31" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137044079</v>
       </c>
       <c r="B32" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>137040113</v>
       </c>
       <c r="B33" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>137040128</v>
       </c>
       <c r="B34" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137040132</v>
       </c>
       <c r="B35" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>137040135</v>
       </c>
       <c r="B36" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>137044081</v>
       </c>
       <c r="B37" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>137040108</v>
       </c>
       <c r="B38" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137040110</v>
       </c>
       <c r="B39" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>137040111</v>
       </c>
       <c r="B40" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>137040156</v>
       </c>
       <c r="B41" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>137040124</v>
       </c>
       <c r="B42" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137040158</v>
       </c>
       <c r="B43" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>137044090</v>
       </c>
       <c r="B44" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>137044091</v>
       </c>
       <c r="B45" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>137040176</v>
       </c>
       <c r="B46" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>137040106</v>
       </c>
       <c r="B47" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>137040109</v>
       </c>
       <c r="B48" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>137040127</v>
       </c>
       <c r="B49" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>137040152</v>
       </c>
       <c r="B50" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>137040177</v>
       </c>
       <c r="B51" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>137040187</v>
       </c>
       <c r="B52" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>137040154</v>
       </c>
       <c r="B53" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137040107</v>
       </c>
       <c r="B54" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>137040118</v>
       </c>
       <c r="B55" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>137040121</v>
       </c>
       <c r="B56" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>137040123</v>
       </c>
       <c r="B57" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>137040126</v>
       </c>
       <c r="B58" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>137040138</v>
       </c>
       <c r="B59" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>137040143</v>
       </c>
       <c r="B60" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>137040145</v>
       </c>
       <c r="B61" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>137040155</v>
       </c>
       <c r="B62" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>137040160</v>
       </c>
       <c r="B63" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>137040166</v>
       </c>
       <c r="B64" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>137040168</v>
       </c>
       <c r="B65" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>137040170</v>
       </c>
       <c r="B66" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>137040178</v>
       </c>
       <c r="B67" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>137040180</v>
       </c>
       <c r="B68" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>137040186</v>
       </c>
       <c r="B69" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>137040188</v>
       </c>
       <c r="B70" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>137040189</v>
       </c>
       <c r="B71" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>137044059</v>
       </c>
       <c r="B72" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>137044060</v>
       </c>
       <c r="B73" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>137044061</v>
       </c>
       <c r="B74" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>137044062</v>
       </c>
       <c r="B75" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>137044064</v>
       </c>
       <c r="B76" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>137044073</v>
       </c>
       <c r="B77" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>137044075</v>
       </c>
       <c r="B78" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>137044080</v>
       </c>
       <c r="B79" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>137044083</v>
       </c>
       <c r="B80" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137044086</v>
       </c>
       <c r="B81" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>137044089</v>
       </c>
       <c r="B82" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>137044092</v>
       </c>
       <c r="B83" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>137044093</v>
       </c>
       <c r="B84" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>137040112</v>
       </c>
       <c r="B85" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>137040146</v>
       </c>
       <c r="B86" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>137040157</v>
       </c>
       <c r="B87" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>137040184</v>
       </c>
       <c r="B88" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>137040185</v>
       </c>
       <c r="B89" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>137044065</v>
       </c>
       <c r="B90" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>137044077</v>
       </c>
       <c r="B91" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>137044087</v>
       </c>
       <c r="B92" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>137044088</v>
       </c>
       <c r="B93" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>137040134</v>
       </c>
       <c r="B94" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>137040136</v>
       </c>
       <c r="B95" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>137040139</v>
       </c>
       <c r="B96" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>137044066</v>
       </c>
       <c r="B97" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>137044071</v>
       </c>
       <c r="B98" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>137044082</v>
       </c>
       <c r="B99" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>137040131</v>
       </c>
       <c r="B100" t="n">
-        <v>92577</v>
+        <v>92581</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
